--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_18-11-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_18-11-2025.xlsx
@@ -558,7 +558,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>£9.83</t>
+          <t>Error: 500 Server Error: Internal Server Error for url: https://materialsmarket.com/products/25mm-celotex-tb4025-pir-insulation-board-2400mm-x-1200mm</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -573,7 +573,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>£11.17</t>
+          <t>Error: 'NoneType' object has no attribute 'find_all'</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -592,23 +592,23 @@
   (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7bd04a235
-	0x7ff7bcda2630
-	0x7ff7bcb316dd
-	0x7ff7bcb8a27e
-	0x7ff7bcb8a58c
-	0x7ff7bcbded77
-	0x7ff7bcbdbaba
-	0x7ff7bcb7b0ed
-	0x7ff7bcb7bf63
-	0x7ff7bd075d60
-	0x7ff7bd06fe8a
-	0x7ff7bd091005
-	0x7ff7bcdbd71e
-	0x7ff7bcdc4e1f
-	0x7ff7bcdab7c4
-	0x7ff7bcdab97f
-	0x7ff7bcd918e8
+	0x7ff73c86a235
+	0x7ff73c5c2630
+	0x7ff73c3516dd
+	0x7ff73c3aa27e
+	0x7ff73c3aa58c
+	0x7ff73c3fed77
+	0x7ff73c3fbaba
+	0x7ff73c39b0ed
+	0x7ff73c39bf63
+	0x7ff73c895d60
+	0x7ff73c88fe8a
+	0x7ff73c8b1005
+	0x7ff73c5dd71e
+	0x7ff73c5e4e1f
+	0x7ff73c5cb7c4
+	0x7ff73c5cb97f
+	0x7ff73c5b18e8
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -616,7 +616,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>£9.77</t>
+          <t>Error: 500 Server Error: Internal Server Error for url: https://www.insulation-online.com/product/celotex-tb4025-25mm/</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -631,7 +631,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: 500 Server Error: Internal Server Error for url: https://www.directinsulation.com/product-page/celotex-tb4025-2400x1200x25mm</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -678,7 +678,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>£11.10</t>
+          <t>Error: 500 Server Error: Internal Server Error for url: https://materialsmarket.com/products/30mm-celotex-tb4030-pir-insulation-board-2400mm-x-1200mm</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>£12.83</t>
+          <t>Error: 'NoneType' object has no attribute 'find_all'</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -712,23 +712,23 @@
   (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7bd04a235
-	0x7ff7bcda2630
-	0x7ff7bcb316dd
-	0x7ff7bcb8a27e
-	0x7ff7bcb8a58c
-	0x7ff7bcbded77
-	0x7ff7bcbdbaba
-	0x7ff7bcb7b0ed
-	0x7ff7bcb7bf63
-	0x7ff7bd075d60
-	0x7ff7bd06fe8a
-	0x7ff7bd091005
-	0x7ff7bcdbd71e
-	0x7ff7bcdc4e1f
-	0x7ff7bcdab7c4
-	0x7ff7bcdab97f
-	0x7ff7bcd918e8
+	0x7ff73c86a235
+	0x7ff73c5c2630
+	0x7ff73c3516dd
+	0x7ff73c3aa27e
+	0x7ff73c3aa58c
+	0x7ff73c3fed77
+	0x7ff73c3fbaba
+	0x7ff73c39b0ed
+	0x7ff73c39bf63
+	0x7ff73c895d60
+	0x7ff73c88fe8a
+	0x7ff73c8b1005
+	0x7ff73c5dd71e
+	0x7ff73c5e4e1f
+	0x7ff73c5cb7c4
+	0x7ff73c5cb97f
+	0x7ff73c5b18e8
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -736,7 +736,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>£11.89</t>
+          <t>Error: 500 Server Error: Internal Server Error for url: https://www.insulation-online.com/product/celotex-tb4030-30mm/</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -751,7 +751,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: 500 Server Error: Internal Server Error for url: https://www.directinsulation.com/product-page/celotex-tb4030-2400x1200x30mm</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -798,7 +798,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>£14.36</t>
+          <t>Error: 500 Server Error: Internal Server Error for url: https://materialsmarket.com/products/40mm-celotex-tb4040-pir-insulation-board-2400mm-x-1200mm</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>£16.46</t>
+          <t>Error: 'NoneType' object has no attribute 'find_all'</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -832,23 +832,23 @@
   (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7bd04a235
-	0x7ff7bcda2630
-	0x7ff7bcb316dd
-	0x7ff7bcb8a27e
-	0x7ff7bcb8a58c
-	0x7ff7bcbded77
-	0x7ff7bcbdbaba
-	0x7ff7bcb7b0ed
-	0x7ff7bcb7bf63
-	0x7ff7bd075d60
-	0x7ff7bd06fe8a
-	0x7ff7bd091005
-	0x7ff7bcdbd71e
-	0x7ff7bcdc4e1f
-	0x7ff7bcdab7c4
-	0x7ff7bcdab97f
-	0x7ff7bcd918e8
+	0x7ff73c86a235
+	0x7ff73c5c2630
+	0x7ff73c3516dd
+	0x7ff73c3aa27e
+	0x7ff73c3aa58c
+	0x7ff73c3fed77
+	0x7ff73c3fbaba
+	0x7ff73c39b0ed
+	0x7ff73c39bf63
+	0x7ff73c895d60
+	0x7ff73c88fe8a
+	0x7ff73c8b1005
+	0x7ff73c5dd71e
+	0x7ff73c5e4e1f
+	0x7ff73c5cb7c4
+	0x7ff73c5cb97f
+	0x7ff73c5b18e8
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -856,7 +856,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>£14.44</t>
+          <t>Error: 500 Server Error: Internal Server Error for url: https://www.insulation-online.com/product/celotex-tb4040-40mm/</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -871,7 +871,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: 500 Server Error: Internal Server Error for url: https://www.directinsulation.com/product-page/celotex-tb4040-2400x1200x40mm</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>£14.63</t>
+          <t>Error: 500 Server Error: Internal Server Error for url: https://materialsmarket.com/products/50mm-celotex-ga4050-pir-insulation-board-2400mm-x-1200mm</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>£16.75</t>
+          <t>Error: 'NoneType' object has no attribute 'find_all'</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -952,23 +952,23 @@
   (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7bd04a235
-	0x7ff7bcda2630
-	0x7ff7bcb316dd
-	0x7ff7bcb8a27e
-	0x7ff7bcb8a58c
-	0x7ff7bcbded77
-	0x7ff7bcbdbaba
-	0x7ff7bcb7b0ed
-	0x7ff7bcb7bf63
-	0x7ff7bd075d60
-	0x7ff7bd06fe8a
-	0x7ff7bd091005
-	0x7ff7bcdbd71e
-	0x7ff7bcdc4e1f
-	0x7ff7bcdab7c4
-	0x7ff7bcdab97f
-	0x7ff7bcd918e8
+	0x7ff73c86a235
+	0x7ff73c5c2630
+	0x7ff73c3516dd
+	0x7ff73c3aa27e
+	0x7ff73c3aa58c
+	0x7ff73c3fed77
+	0x7ff73c3fbaba
+	0x7ff73c39b0ed
+	0x7ff73c39bf63
+	0x7ff73c895d60
+	0x7ff73c88fe8a
+	0x7ff73c8b1005
+	0x7ff73c5dd71e
+	0x7ff73c5e4e1f
+	0x7ff73c5cb7c4
+	0x7ff73c5cb97f
+	0x7ff73c5b18e8
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -976,7 +976,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>£15.4</t>
+          <t>Error: 500 Server Error: Internal Server Error for url: https://www.insulation-online.com/product/celotex-ga4050-50mm/</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -991,7 +991,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: 500 Server Error: Internal Server Error for url: https://www.directinsulation.com/product-page/celotex-ga4050-2400x1200x50mm</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -1038,7 +1038,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>£18.61</t>
+          <t>Error: 500 Server Error: Internal Server Error for url: https://materialsmarket.com/products/60mm-celotex-ga4060-pir-insulation-board-2400mm-x-1200mm</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1053,7 +1053,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>£21.46</t>
+          <t>Error: 'NoneType' object has no attribute 'find_all'</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1072,23 +1072,23 @@
   (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7bd04a235
-	0x7ff7bcda2630
-	0x7ff7bcb316dd
-	0x7ff7bcb8a27e
-	0x7ff7bcb8a58c
-	0x7ff7bcbded77
-	0x7ff7bcbdbaba
-	0x7ff7bcb7b0ed
-	0x7ff7bcb7bf63
-	0x7ff7bd075d60
-	0x7ff7bd06fe8a
-	0x7ff7bd091005
-	0x7ff7bcdbd71e
-	0x7ff7bcdc4e1f
-	0x7ff7bcdab7c4
-	0x7ff7bcdab97f
-	0x7ff7bcd918e8
+	0x7ff73c86a235
+	0x7ff73c5c2630
+	0x7ff73c3516dd
+	0x7ff73c3aa27e
+	0x7ff73c3aa58c
+	0x7ff73c3fed77
+	0x7ff73c3fbaba
+	0x7ff73c39b0ed
+	0x7ff73c39bf63
+	0x7ff73c895d60
+	0x7ff73c88fe8a
+	0x7ff73c8b1005
+	0x7ff73c5dd71e
+	0x7ff73c5e4e1f
+	0x7ff73c5cb7c4
+	0x7ff73c5cb97f
+	0x7ff73c5b18e8
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>£19.19</t>
+          <t>Error: 500 Server Error: Internal Server Error for url: https://www.insulation-online.com/product/celotex-ga4060-60mm/</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: 500 Server Error: Internal Server Error for url: https://www.directinsulation.com/product-page/celotex-ga4060-2400x1200x60mm</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1158,7 +1158,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>£20.30</t>
+          <t>Error: 500 Server Error: Internal Server Error for url: https://materialsmarket.com/products/70mm-celotex-ga4070-pir-insulation-board-2400mm-x-1200mm</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1173,7 +1173,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>£23.15</t>
+          <t>Error: 'NoneType' object has no attribute 'find_all'</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1192,23 +1192,23 @@
   (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7bd04a235
-	0x7ff7bcda2630
-	0x7ff7bcb316dd
-	0x7ff7bcb8a27e
-	0x7ff7bcb8a58c
-	0x7ff7bcbded77
-	0x7ff7bcbdbaba
-	0x7ff7bcb7b0ed
-	0x7ff7bcb7bf63
-	0x7ff7bd075d60
-	0x7ff7bd06fe8a
-	0x7ff7bd091005
-	0x7ff7bcdbd71e
-	0x7ff7bcdc4e1f
-	0x7ff7bcdab7c4
-	0x7ff7bcdab97f
-	0x7ff7bcd918e8
+	0x7ff73c86a235
+	0x7ff73c5c2630
+	0x7ff73c3516dd
+	0x7ff73c3aa27e
+	0x7ff73c3aa58c
+	0x7ff73c3fed77
+	0x7ff73c3fbaba
+	0x7ff73c39b0ed
+	0x7ff73c39bf63
+	0x7ff73c895d60
+	0x7ff73c88fe8a
+	0x7ff73c8b1005
+	0x7ff73c5dd71e
+	0x7ff73c5e4e1f
+	0x7ff73c5cb7c4
+	0x7ff73c5cb97f
+	0x7ff73c5b18e8
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>£21.62</t>
+          <t>Error: 500 Server Error: Internal Server Error for url: https://www.insulation-online.com/product/celotex-ga4070-70mm/</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: 500 Server Error: Internal Server Error for url: https://www.directinsulation.com/product-page/celotex-ga4070-2400x1200x70mm</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>£20.49</t>
+          <t>Error: 500 Server Error: Internal Server Error for url: https://materialsmarket.com/products/75mm-celotex-ga4075-pir-insulation-board-2400mm-x-1200mm</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>£23.50</t>
+          <t>Error: 'NoneType' object has no attribute 'find_all'</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1312,23 +1312,23 @@
   (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7bd04a235
-	0x7ff7bcda2630
-	0x7ff7bcb316dd
-	0x7ff7bcb8a27e
-	0x7ff7bcb8a58c
-	0x7ff7bcbded77
-	0x7ff7bcbdbaba
-	0x7ff7bcb7b0ed
-	0x7ff7bcb7bf63
-	0x7ff7bd075d60
-	0x7ff7bd06fe8a
-	0x7ff7bd091005
-	0x7ff7bcdbd71e
-	0x7ff7bcdc4e1f
-	0x7ff7bcdab7c4
-	0x7ff7bcdab97f
-	0x7ff7bcd918e8
+	0x7ff73c86a235
+	0x7ff73c5c2630
+	0x7ff73c3516dd
+	0x7ff73c3aa27e
+	0x7ff73c3aa58c
+	0x7ff73c3fed77
+	0x7ff73c3fbaba
+	0x7ff73c39b0ed
+	0x7ff73c39bf63
+	0x7ff73c895d60
+	0x7ff73c88fe8a
+	0x7ff73c8b1005
+	0x7ff73c5dd71e
+	0x7ff73c5e4e1f
+	0x7ff73c5cb7c4
+	0x7ff73c5cb97f
+	0x7ff73c5b18e8
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>£20.97</t>
+          <t>Error: 500 Server Error: Internal Server Error for url: https://www.insulation-online.com/product/celotex-ga4075-75mm/</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1351,7 +1351,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: 500 Server Error: Internal Server Error for url: https://www.directinsulation.com/product-page/celotex-ga4075-2400x1200x75mm</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>£23.51</t>
+          <t>Error: 500 Server Error: Internal Server Error for url: https://materialsmarket.com/products/80mm-celotex-ga4080-pir-insulation-board-2400mm-x-1200mm</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>£26.79</t>
+          <t>Error: 'NoneType' object has no attribute 'find_all'</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1432,23 +1432,23 @@
   (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7bd04a235
-	0x7ff7bcda2630
-	0x7ff7bcb316dd
-	0x7ff7bcb8a27e
-	0x7ff7bcb8a58c
-	0x7ff7bcbded77
-	0x7ff7bcbdbaba
-	0x7ff7bcb7b0ed
-	0x7ff7bcb7bf63
-	0x7ff7bd075d60
-	0x7ff7bd06fe8a
-	0x7ff7bd091005
-	0x7ff7bcdbd71e
-	0x7ff7bcdc4e1f
-	0x7ff7bcdab7c4
-	0x7ff7bcdab97f
-	0x7ff7bcd918e8
+	0x7ff73c86a235
+	0x7ff73c5c2630
+	0x7ff73c3516dd
+	0x7ff73c3aa27e
+	0x7ff73c3aa58c
+	0x7ff73c3fed77
+	0x7ff73c3fbaba
+	0x7ff73c39b0ed
+	0x7ff73c39bf63
+	0x7ff73c895d60
+	0x7ff73c88fe8a
+	0x7ff73c8b1005
+	0x7ff73c5dd71e
+	0x7ff73c5e4e1f
+	0x7ff73c5cb7c4
+	0x7ff73c5cb97f
+	0x7ff73c5b18e8
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>£23.83</t>
+          <t>Error: 500 Server Error: Internal Server Error for url: https://www.insulation-online.com/product/celotex-ga4080-80mm/</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: 500 Server Error: Internal Server Error for url: https://www.directinsulation.com/product-page/celotex-ga4080-2400x1200x80mm</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -1518,7 +1518,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>£25.49</t>
+          <t>Error: 500 Server Error: Internal Server Error for url: https://materialsmarket.com/products/90mm-celotex-ga4090-pir-insulation-board-2400mm-x-1200mm</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1533,7 +1533,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>£29.33</t>
+          <t>Error: 'NoneType' object has no attribute 'find_all'</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1552,23 +1552,23 @@
   (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7bd04a235
-	0x7ff7bcda2630
-	0x7ff7bcb316dd
-	0x7ff7bcb8a27e
-	0x7ff7bcb8a58c
-	0x7ff7bcbded77
-	0x7ff7bcbdbaba
-	0x7ff7bcb7b0ed
-	0x7ff7bcb7bf63
-	0x7ff7bd075d60
-	0x7ff7bd06fe8a
-	0x7ff7bd091005
-	0x7ff7bcdbd71e
-	0x7ff7bcdc4e1f
-	0x7ff7bcdab7c4
-	0x7ff7bcdab97f
-	0x7ff7bcd918e8
+	0x7ff73c86a235
+	0x7ff73c5c2630
+	0x7ff73c3516dd
+	0x7ff73c3aa27e
+	0x7ff73c3aa58c
+	0x7ff73c3fed77
+	0x7ff73c3fbaba
+	0x7ff73c39b0ed
+	0x7ff73c39bf63
+	0x7ff73c895d60
+	0x7ff73c88fe8a
+	0x7ff73c8b1005
+	0x7ff73c5dd71e
+	0x7ff73c5e4e1f
+	0x7ff73c5cb7c4
+	0x7ff73c5cb97f
+	0x7ff73c5b18e8
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -1576,7 +1576,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>£26.35</t>
+          <t>Error: 500 Server Error: Internal Server Error for url: https://www.insulation-online.com/product/celotex-ga4090-90mm/</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1591,7 +1591,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: 500 Server Error: Internal Server Error for url: https://www.directinsulation.com/product-page/celotex-ga4090-2400x1200x90mm</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -1638,7 +1638,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>£25.25</t>
+          <t>Error: 500 Server Error: Internal Server Error for url: https://materialsmarket.com/products/100mm-celotex-ga4100-pir-insulation-board-2400mm-x-1200mm</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>£27.29</t>
+          <t>Error: 'NoneType' object has no attribute 'find_all'</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1672,23 +1672,23 @@
   (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7bd04a235
-	0x7ff7bcda2630
-	0x7ff7bcb316dd
-	0x7ff7bcb8a27e
-	0x7ff7bcb8a58c
-	0x7ff7bcbded77
-	0x7ff7bcbdbaba
-	0x7ff7bcb7b0ed
-	0x7ff7bcb7bf63
-	0x7ff7bd075d60
-	0x7ff7bd06fe8a
-	0x7ff7bd091005
-	0x7ff7bcdbd71e
-	0x7ff7bcdc4e1f
-	0x7ff7bcdab7c4
-	0x7ff7bcdab97f
-	0x7ff7bcd918e8
+	0x7ff73c86a235
+	0x7ff73c5c2630
+	0x7ff73c3516dd
+	0x7ff73c3aa27e
+	0x7ff73c3aa58c
+	0x7ff73c3fed77
+	0x7ff73c3fbaba
+	0x7ff73c39b0ed
+	0x7ff73c39bf63
+	0x7ff73c895d60
+	0x7ff73c88fe8a
+	0x7ff73c8b1005
+	0x7ff73c5dd71e
+	0x7ff73c5e4e1f
+	0x7ff73c5cb7c4
+	0x7ff73c5cb97f
+	0x7ff73c5b18e8
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>£26.35</t>
+          <t>Error: 500 Server Error: Internal Server Error for url: https://www.insulation-online.com/product/celotex-ga4100-100mm/</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: 500 Server Error: Internal Server Error for url: https://www.directinsulation.com/product-page/celotex-ga4100-2400x1200x100mm</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>£33.17</t>
+          <t>Error: 500 Server Error: Internal Server Error for url: https://materialsmarket.com/products/110mm-celotex-xr4110-pir-insulation-board-2400mm-x-1200mm</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>£41.79</t>
+          <t>Error: 'NoneType' object has no attribute 'find_all'</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1792,23 +1792,23 @@
   (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7bd04a235
-	0x7ff7bcda2630
-	0x7ff7bcb316dd
-	0x7ff7bcb8a27e
-	0x7ff7bcb8a58c
-	0x7ff7bcbded77
-	0x7ff7bcbdbaba
-	0x7ff7bcb7b0ed
-	0x7ff7bcb7bf63
-	0x7ff7bd075d60
-	0x7ff7bd06fe8a
-	0x7ff7bd091005
-	0x7ff7bcdbd71e
-	0x7ff7bcdc4e1f
-	0x7ff7bcdab7c4
-	0x7ff7bcdab97f
-	0x7ff7bcd918e8
+	0x7ff73c86a235
+	0x7ff73c5c2630
+	0x7ff73c3516dd
+	0x7ff73c3aa27e
+	0x7ff73c3aa58c
+	0x7ff73c3fed77
+	0x7ff73c3fbaba
+	0x7ff73c39b0ed
+	0x7ff73c39bf63
+	0x7ff73c895d60
+	0x7ff73c88fe8a
+	0x7ff73c8b1005
+	0x7ff73c5dd71e
+	0x7ff73c5e4e1f
+	0x7ff73c5cb7c4
+	0x7ff73c5cb97f
+	0x7ff73c5b18e8
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -1816,7 +1816,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>£31.88</t>
+          <t>Error: 500 Server Error: Internal Server Error for url: https://www.insulation-online.com/product/celotex-xr4110-110mm/</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1831,7 +1831,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: 500 Server Error: Internal Server Error for url: https://www.directinsulation.com/product-page/celotex-xr4110-insulation-2400x1200x110mm</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1878,7 +1878,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>£30.79</t>
+          <t>Error: 500 Server Error: Internal Server Error for url: https://materialsmarket.com/products/120mm-celotex-xr4120-pir-insulation-board-2400mm-x-1200mm</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>£35.08</t>
+          <t>Error: 'NoneType' object has no attribute 'find_all'</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1912,23 +1912,23 @@
   (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7bd04a235
-	0x7ff7bcda2630
-	0x7ff7bcb316dd
-	0x7ff7bcb8a27e
-	0x7ff7bcb8a58c
-	0x7ff7bcbded77
-	0x7ff7bcbdbaba
-	0x7ff7bcb7b0ed
-	0x7ff7bcb7bf63
-	0x7ff7bd075d60
-	0x7ff7bd06fe8a
-	0x7ff7bd091005
-	0x7ff7bcdbd71e
-	0x7ff7bcdc4e1f
-	0x7ff7bcdab7c4
-	0x7ff7bcdab97f
-	0x7ff7bcd918e8
+	0x7ff73c86a235
+	0x7ff73c5c2630
+	0x7ff73c3516dd
+	0x7ff73c3aa27e
+	0x7ff73c3aa58c
+	0x7ff73c3fed77
+	0x7ff73c3fbaba
+	0x7ff73c39b0ed
+	0x7ff73c39bf63
+	0x7ff73c895d60
+	0x7ff73c88fe8a
+	0x7ff73c8b1005
+	0x7ff73c5dd71e
+	0x7ff73c5e4e1f
+	0x7ff73c5cb7c4
+	0x7ff73c5cb97f
+	0x7ff73c5b18e8
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>£32.98</t>
+          <t>Error: 500 Server Error: Internal Server Error for url: https://www.insulation-online.com/product/celotex-xr4120-120mm/</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: 500 Server Error: Internal Server Error for url: https://www.directinsulation.com/product-page/celotex-xr4120-2400x1200x120mm</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -1998,7 +1998,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>£39.09</t>
+          <t>Error: 500 Server Error: Internal Server Error for url: https://materialsmarket.com/products/130mm-celotex-xr4130-pir-insulation-board-2400mm-x-1200mm</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>£46.74</t>
+          <t>Error: 'NoneType' object has no attribute 'find_all'</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -2032,23 +2032,23 @@
   (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7bd04a235
-	0x7ff7bcda2630
-	0x7ff7bcb316dd
-	0x7ff7bcb8a27e
-	0x7ff7bcb8a58c
-	0x7ff7bcbded77
-	0x7ff7bcbdbaba
-	0x7ff7bcb7b0ed
-	0x7ff7bcb7bf63
-	0x7ff7bd075d60
-	0x7ff7bd06fe8a
-	0x7ff7bd091005
-	0x7ff7bcdbd71e
-	0x7ff7bcdc4e1f
-	0x7ff7bcdab7c4
-	0x7ff7bcdab97f
-	0x7ff7bcd918e8
+	0x7ff73c86a235
+	0x7ff73c5c2630
+	0x7ff73c3516dd
+	0x7ff73c3aa27e
+	0x7ff73c3aa58c
+	0x7ff73c3fed77
+	0x7ff73c3fbaba
+	0x7ff73c39b0ed
+	0x7ff73c39bf63
+	0x7ff73c895d60
+	0x7ff73c88fe8a
+	0x7ff73c8b1005
+	0x7ff73c5dd71e
+	0x7ff73c5e4e1f
+	0x7ff73c5cb7c4
+	0x7ff73c5cb97f
+	0x7ff73c5b18e8
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -2056,7 +2056,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>£37.39</t>
+          <t>Error: 500 Server Error: Internal Server Error for url: https://www.insulation-online.com/product/celotex-xr4130-130mm/</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: 500 Server Error: Internal Server Error for url: https://www.directinsulation.com/product-page/celotex-xr4130-2400x1200x130mm</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -2118,7 +2118,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>£37.94</t>
+          <t>Error: 500 Server Error: Internal Server Error for url: https://materialsmarket.com/products/140mm-celotex-xr4140-pir-insulation-board-2400mm-x-1200mm</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2133,7 +2133,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>£47.29</t>
+          <t>Error: 'NoneType' object has no attribute 'find_all'</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -2152,23 +2152,23 @@
   (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7bd04a235
-	0x7ff7bcda2630
-	0x7ff7bcb316dd
-	0x7ff7bcb8a27e
-	0x7ff7bcb8a58c
-	0x7ff7bcbded77
-	0x7ff7bcbdbaba
-	0x7ff7bcb7b0ed
-	0x7ff7bcb7bf63
-	0x7ff7bd075d60
-	0x7ff7bd06fe8a
-	0x7ff7bd091005
-	0x7ff7bcdbd71e
-	0x7ff7bcdc4e1f
-	0x7ff7bcdab7c4
-	0x7ff7bcdab97f
-	0x7ff7bcd918e8
+	0x7ff73c86a235
+	0x7ff73c5c2630
+	0x7ff73c3516dd
+	0x7ff73c3aa27e
+	0x7ff73c3aa58c
+	0x7ff73c3fed77
+	0x7ff73c3fbaba
+	0x7ff73c39b0ed
+	0x7ff73c39bf63
+	0x7ff73c895d60
+	0x7ff73c88fe8a
+	0x7ff73c8b1005
+	0x7ff73c5dd71e
+	0x7ff73c5e4e1f
+	0x7ff73c5cb7c4
+	0x7ff73c5cb97f
+	0x7ff73c5b18e8
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>£40.35</t>
+          <t>Error: 500 Server Error: Internal Server Error for url: https://www.insulation-online.com/product/celotex-xr4140-140mm/</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: 500 Server Error: Internal Server Error for url: https://www.directinsulation.com/product-page/celotex-xr4140-2400x1200x140mm</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -2238,7 +2238,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>£37.72</t>
+          <t>Error: 500 Server Error: Internal Server Error for url: https://materialsmarket.com/products/150mm-celotex-xr4150-pir-insulation-board-2400mm-x-1200mm</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>£43.58</t>
+          <t>Error: 'NoneType' object has no attribute 'find_all'</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -2272,23 +2272,23 @@
   (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7bd04a235
-	0x7ff7bcda2630
-	0x7ff7bcb316dd
-	0x7ff7bcb8a27e
-	0x7ff7bcb8a58c
-	0x7ff7bcbded77
-	0x7ff7bcbdbaba
-	0x7ff7bcb7b0ed
-	0x7ff7bcb7bf63
-	0x7ff7bd075d60
-	0x7ff7bd06fe8a
-	0x7ff7bd091005
-	0x7ff7bcdbd71e
-	0x7ff7bcdc4e1f
-	0x7ff7bcdab7c4
-	0x7ff7bcdab97f
-	0x7ff7bcd918e8
+	0x7ff73c86a235
+	0x7ff73c5c2630
+	0x7ff73c3516dd
+	0x7ff73c3aa27e
+	0x7ff73c3aa58c
+	0x7ff73c3fed77
+	0x7ff73c3fbaba
+	0x7ff73c39b0ed
+	0x7ff73c39bf63
+	0x7ff73c895d60
+	0x7ff73c88fe8a
+	0x7ff73c8b1005
+	0x7ff73c5dd71e
+	0x7ff73c5e4e1f
+	0x7ff73c5cb7c4
+	0x7ff73c5cb97f
+	0x7ff73c5b18e8
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -2296,7 +2296,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>£39.6</t>
+          <t>Error: 500 Server Error: Internal Server Error for url: https://www.insulation-online.com/product/celotex-xr4150-150mm/</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -2311,7 +2311,7 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: 500 Server Error: Internal Server Error for url: https://www.directinsulation.com/product-page/celotex-xr4150-2400x1200x150mm</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -2358,7 +2358,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>£877.92</t>
+          <t>Error: 500 Server Error: Internal Server Error for url: https://materialsmarket.com/products/165mm-celotex-xr4165-pir-insulation-board-2400mm-x-1200mm</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2373,7 +2373,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>£857.88</t>
+          <t>Error: 'NoneType' object has no attribute 'find_all'</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -2393,7 +2393,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>£634.53</t>
+          <t>Error: 500 Server Error: Internal Server Error for url: https://www.insulation-online.com/product/celotex-xr4165-165mm/</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -2455,7 +2455,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>£960.0</t>
+          <t>Error: 500 Server Error: Internal Server Error for url: https://materialsmarket.com/products/200mm-celotex-xr4200-pir-insulation-board-2400mm-x-1200mm</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>£1029.48</t>
+          <t>Error: 'NoneType' object has no attribute 'find_all'</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -2489,23 +2489,23 @@
   (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7bd04a235
-	0x7ff7bcda2630
-	0x7ff7bcb316dd
-	0x7ff7bcb8a27e
-	0x7ff7bcb8a58c
-	0x7ff7bcbded77
-	0x7ff7bcbdbaba
-	0x7ff7bcb7b0ed
-	0x7ff7bcb7bf63
-	0x7ff7bd075d60
-	0x7ff7bd06fe8a
-	0x7ff7bd091005
-	0x7ff7bcdbd71e
-	0x7ff7bcdc4e1f
-	0x7ff7bcdab7c4
-	0x7ff7bcdab97f
-	0x7ff7bcd918e8
+	0x7ff73c86a235
+	0x7ff73c5c2630
+	0x7ff73c3516dd
+	0x7ff73c3aa27e
+	0x7ff73c3aa58c
+	0x7ff73c3fed77
+	0x7ff73c3fbaba
+	0x7ff73c39b0ed
+	0x7ff73c39bf63
+	0x7ff73c895d60
+	0x7ff73c88fe8a
+	0x7ff73c8b1005
+	0x7ff73c5dd71e
+	0x7ff73c5e4e1f
+	0x7ff73c5cb7c4
+	0x7ff73c5cb97f
+	0x7ff73c5b18e8
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -2513,7 +2513,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>£853.62</t>
+          <t>Error: 500 Server Error: Internal Server Error for url: https://www.insulation-online.com/product/celotex-xr4200-200mm/</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -2575,7 +2575,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>£28.12</t>
+          <t>Error: 500 Server Error: Internal Server Error for url: https://materialsmarket.com/products/37-5mm-celotex-pl4025-insulated-plasterboard-2400mm-x-1200mm</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2590,7 +2590,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>£37.39</t>
+          <t>Error: 'NoneType' object has no attribute 'find_all'</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -2609,23 +2609,23 @@
   (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7bd04a235
-	0x7ff7bcda2630
-	0x7ff7bcb316dd
-	0x7ff7bcb8a27e
-	0x7ff7bcb8a58c
-	0x7ff7bcbded77
-	0x7ff7bcbdbaba
-	0x7ff7bcb7b0ed
-	0x7ff7bcb7bf63
-	0x7ff7bd075d60
-	0x7ff7bd06fe8a
-	0x7ff7bd091005
-	0x7ff7bcdbd71e
-	0x7ff7bcdc4e1f
-	0x7ff7bcdab7c4
-	0x7ff7bcdab97f
-	0x7ff7bcd918e8
+	0x7ff73c86a235
+	0x7ff73c5c2630
+	0x7ff73c3516dd
+	0x7ff73c3aa27e
+	0x7ff73c3aa58c
+	0x7ff73c3fed77
+	0x7ff73c3fbaba
+	0x7ff73c39b0ed
+	0x7ff73c39bf63
+	0x7ff73c895d60
+	0x7ff73c88fe8a
+	0x7ff73c8b1005
+	0x7ff73c5dd71e
+	0x7ff73c5e4e1f
+	0x7ff73c5cb7c4
+	0x7ff73c5cb97f
+	0x7ff73c5b18e8
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -2633,7 +2633,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>£36.95</t>
+          <t>Error: 500 Server Error: Internal Server Error for url: https://www.insulation-online.com/product/celotex-pl4025-38mm/</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: 500 Server Error: Internal Server Error for url: https://www.directinsulation.com/product-page/celotex-pl4025-ins-plasterboard-25mm-12-5mm</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -2695,7 +2695,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>£33.87</t>
+          <t>Error: 500 Server Error: Internal Server Error for url: https://materialsmarket.com/products/52-5mm-celotex-pl4040-insulated-plasterboard-2400mm-x-1200mm</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2710,7 +2710,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>£47.29</t>
+          <t>Error: 'NoneType' object has no attribute 'find_all'</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -2729,23 +2729,23 @@
   (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7bd04a235
-	0x7ff7bcda2630
-	0x7ff7bcb316dd
-	0x7ff7bcb8a27e
-	0x7ff7bcb8a58c
-	0x7ff7bcbded77
-	0x7ff7bcbdbaba
-	0x7ff7bcb7b0ed
-	0x7ff7bcb7bf63
-	0x7ff7bd075d60
-	0x7ff7bd06fe8a
-	0x7ff7bd091005
-	0x7ff7bcdbd71e
-	0x7ff7bcdc4e1f
-	0x7ff7bcdab7c4
-	0x7ff7bcdab97f
-	0x7ff7bcd918e8
+	0x7ff73c86a235
+	0x7ff73c5c2630
+	0x7ff73c3516dd
+	0x7ff73c3aa27e
+	0x7ff73c3aa58c
+	0x7ff73c3fed77
+	0x7ff73c3fbaba
+	0x7ff73c39b0ed
+	0x7ff73c39bf63
+	0x7ff73c895d60
+	0x7ff73c88fe8a
+	0x7ff73c8b1005
+	0x7ff73c5dd71e
+	0x7ff73c5e4e1f
+	0x7ff73c5cb7c4
+	0x7ff73c5cb97f
+	0x7ff73c5b18e8
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>£44.24</t>
+          <t>Error: 500 Server Error: Internal Server Error for url: https://www.insulation-online.com/product/celotex-pl4040-53mm/</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -2815,7 +2815,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>£36.81</t>
+          <t>Error: 500 Server Error: Internal Server Error for url: https://materialsmarket.com/products/62-5mm-celotex-pl4050-insulated-plasterboard-2400mm-x-1200mm</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2830,7 +2830,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>£49.49</t>
+          <t>Error: 'NoneType' object has no attribute 'find_all'</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -2849,23 +2849,23 @@
   (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7bd04a235
-	0x7ff7bcda2630
-	0x7ff7bcb316dd
-	0x7ff7bcb8a27e
-	0x7ff7bcb8a58c
-	0x7ff7bcbded77
-	0x7ff7bcbdbaba
-	0x7ff7bcb7b0ed
-	0x7ff7bcb7bf63
-	0x7ff7bd075d60
-	0x7ff7bd06fe8a
-	0x7ff7bd091005
-	0x7ff7bcdbd71e
-	0x7ff7bcdc4e1f
-	0x7ff7bcdab7c4
-	0x7ff7bcdab97f
-	0x7ff7bcd918e8
+	0x7ff73c86a235
+	0x7ff73c5c2630
+	0x7ff73c3516dd
+	0x7ff73c3aa27e
+	0x7ff73c3aa58c
+	0x7ff73c3fed77
+	0x7ff73c3fbaba
+	0x7ff73c39b0ed
+	0x7ff73c39bf63
+	0x7ff73c895d60
+	0x7ff73c88fe8a
+	0x7ff73c8b1005
+	0x7ff73c5dd71e
+	0x7ff73c5e4e1f
+	0x7ff73c5cb7c4
+	0x7ff73c5cb97f
+	0x7ff73c5b18e8
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -2873,7 +2873,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>£52.32</t>
+          <t>Error: 500 Server Error: Internal Server Error for url: https://www.insulation-online.com/product/celotex-pl4050-63mm/</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -2888,7 +2888,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: 500 Server Error: Internal Server Error for url: https://www.directinsulation.com/product-page/celotex-pl4050-ins-plasterboard-50mm-12-5mm</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -2935,7 +2935,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>£41.98</t>
+          <t>Error: 500 Server Error: Internal Server Error for url: https://materialsmarket.com/products/72-5mm-celotex-pl4060-insulated-plasterboard-2400mm-x-1200mm</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2950,7 +2950,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>£54.99</t>
+          <t>Error: 'NoneType' object has no attribute 'find_all'</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -2969,23 +2969,23 @@
   (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7bd04a235
-	0x7ff7bcda2630
-	0x7ff7bcb316dd
-	0x7ff7bcb8a27e
-	0x7ff7bcb8a58c
-	0x7ff7bcbded77
-	0x7ff7bcbdbaba
-	0x7ff7bcb7b0ed
-	0x7ff7bcb7bf63
-	0x7ff7bd075d60
-	0x7ff7bd06fe8a
-	0x7ff7bd091005
-	0x7ff7bcdbd71e
-	0x7ff7bcdc4e1f
-	0x7ff7bcdab7c4
-	0x7ff7bcdab97f
-	0x7ff7bcd918e8
+	0x7ff73c86a235
+	0x7ff73c5c2630
+	0x7ff73c3516dd
+	0x7ff73c3aa27e
+	0x7ff73c3aa58c
+	0x7ff73c3fed77
+	0x7ff73c3fbaba
+	0x7ff73c39b0ed
+	0x7ff73c39bf63
+	0x7ff73c895d60
+	0x7ff73c88fe8a
+	0x7ff73c8b1005
+	0x7ff73c5dd71e
+	0x7ff73c5e4e1f
+	0x7ff73c5cb7c4
+	0x7ff73c5cb97f
+	0x7ff73c5b18e8
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -2993,7 +2993,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>£55.49</t>
+          <t>Error: 500 Server Error: Internal Server Error for url: https://www.insulation-online.com/product/celotex-pl4060-73mm/</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -3055,7 +3055,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>£49.60</t>
+          <t>Error: 500 Server Error: Internal Server Error for url: https://materialsmarket.com/products/50mm-celotex-cavity-wall-insulation-board-1200mm-x-450mm-5-94m2-pack</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3070,7 +3070,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>£78.54</t>
+          <t>Error: 'NoneType' object has no attribute 'find_all'</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -3089,23 +3089,23 @@
   (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7bd04a235
-	0x7ff7bcda2630
-	0x7ff7bcb316dd
-	0x7ff7bcb8a27e
-	0x7ff7bcb8a58c
-	0x7ff7bcbded77
-	0x7ff7bcbdbaba
-	0x7ff7bcb7b0ed
-	0x7ff7bcb7bf63
-	0x7ff7bd075d60
-	0x7ff7bd06fe8a
-	0x7ff7bd091005
-	0x7ff7bcdbd71e
-	0x7ff7bcdc4e1f
-	0x7ff7bcdab7c4
-	0x7ff7bcdab97f
-	0x7ff7bcd918e8
+	0x7ff73c86a235
+	0x7ff73c5c2630
+	0x7ff73c3516dd
+	0x7ff73c3aa27e
+	0x7ff73c3aa58c
+	0x7ff73c3fed77
+	0x7ff73c3fbaba
+	0x7ff73c39b0ed
+	0x7ff73c39bf63
+	0x7ff73c895d60
+	0x7ff73c88fe8a
+	0x7ff73c8b1005
+	0x7ff73c5dd71e
+	0x7ff73c5e4e1f
+	0x7ff73c5cb7c4
+	0x7ff73c5cb97f
+	0x7ff73c5b18e8
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -3113,7 +3113,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>£41.25</t>
+          <t>Error: 500 Server Error: Internal Server Error for url: https://www.insulation-online.com/product/celotex-cw4050-50mm/</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -3128,7 +3128,7 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: 500 Server Error: Internal Server Error for url: https://www.directinsulation.com/product-page/celotex-cavity-insulation-cw4050-450mm-x-1200mm-pack-of-11</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>£48.04</t>
+          <t>Error: 500 Server Error: Internal Server Error for url: https://materialsmarket.com/products/75mm-celotex-cavity-wall-insulation-board-1200mm-x-450mm-4-32m2-pack</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3190,7 +3190,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>£85.44</t>
+          <t>Error: 'NoneType' object has no attribute 'find_all'</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -3209,23 +3209,23 @@
   (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7bd04a235
-	0x7ff7bcda2630
-	0x7ff7bcb316dd
-	0x7ff7bcb8a27e
-	0x7ff7bcb8a58c
-	0x7ff7bcbded77
-	0x7ff7bcbdbaba
-	0x7ff7bcb7b0ed
-	0x7ff7bcb7bf63
-	0x7ff7bd075d60
-	0x7ff7bd06fe8a
-	0x7ff7bd091005
-	0x7ff7bcdbd71e
-	0x7ff7bcdc4e1f
-	0x7ff7bcdab7c4
-	0x7ff7bcdab97f
-	0x7ff7bcd918e8
+	0x7ff73c86a235
+	0x7ff73c5c2630
+	0x7ff73c3516dd
+	0x7ff73c3aa27e
+	0x7ff73c3aa58c
+	0x7ff73c3fed77
+	0x7ff73c3fbaba
+	0x7ff73c39b0ed
+	0x7ff73c39bf63
+	0x7ff73c895d60
+	0x7ff73c88fe8a
+	0x7ff73c8b1005
+	0x7ff73c5dd71e
+	0x7ff73c5e4e1f
+	0x7ff73c5cb7c4
+	0x7ff73c5cb97f
+	0x7ff73c5b18e8
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -3233,7 +3233,7 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>£39.38</t>
+          <t>Error: 500 Server Error: Internal Server Error for url: https://www.insulation-online.com/product/celotex-cw4075-75mm/</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -3248,7 +3248,7 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: 500 Server Error: Internal Server Error for url: https://www.directinsulation.com/product-page/celotex-cavity-cw4075-450mm-x-1200mm-pack-of-8</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -3329,23 +3329,23 @@
   (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7bd04a235
-	0x7ff7bcda2630
-	0x7ff7bcb316dd
-	0x7ff7bcb8a27e
-	0x7ff7bcb8a58c
-	0x7ff7bcbded77
-	0x7ff7bcbdbaba
-	0x7ff7bcb7b0ed
-	0x7ff7bcb7bf63
-	0x7ff7bd075d60
-	0x7ff7bd06fe8a
-	0x7ff7bd091005
-	0x7ff7bcdbd71e
-	0x7ff7bcdc4e1f
-	0x7ff7bcdab7c4
-	0x7ff7bcdab97f
-	0x7ff7bcd918e8
+	0x7ff73c86a235
+	0x7ff73c5c2630
+	0x7ff73c3516dd
+	0x7ff73c3aa27e
+	0x7ff73c3aa58c
+	0x7ff73c3fed77
+	0x7ff73c3fbaba
+	0x7ff73c39b0ed
+	0x7ff73c39bf63
+	0x7ff73c895d60
+	0x7ff73c88fe8a
+	0x7ff73c8b1005
+	0x7ff73c5dd71e
+	0x7ff73c5e4e1f
+	0x7ff73c5cb7c4
+	0x7ff73c5cb97f
+	0x7ff73c5b18e8
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -3415,7 +3415,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>£46.50</t>
+          <t>Error: 500 Server Error: Internal Server Error for url: https://materialsmarket.com/products/100mm-celotex-cavity-wall-insulation-board-1200mm-x-450mm-3-24m2-pack</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3425,12 +3425,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>£43.19</t>
+          <t>£42.88</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>£81.9</t>
+          <t>Error: 'NoneType' object has no attribute 'find_all'</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -3449,23 +3449,23 @@
   (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7bd04a235
-	0x7ff7bcda2630
-	0x7ff7bcb316dd
-	0x7ff7bcb8a27e
-	0x7ff7bcb8a58c
-	0x7ff7bcbded77
-	0x7ff7bcbdbaba
-	0x7ff7bcb7b0ed
-	0x7ff7bcb7bf63
-	0x7ff7bd075d60
-	0x7ff7bd06fe8a
-	0x7ff7bd091005
-	0x7ff7bcdbd71e
-	0x7ff7bcdc4e1f
-	0x7ff7bcdab7c4
-	0x7ff7bcdab97f
-	0x7ff7bcd918e8
+	0x7ff73c86a235
+	0x7ff73c5c2630
+	0x7ff73c3516dd
+	0x7ff73c3aa27e
+	0x7ff73c3aa58c
+	0x7ff73c3fed77
+	0x7ff73c3fbaba
+	0x7ff73c39b0ed
+	0x7ff73c39bf63
+	0x7ff73c895d60
+	0x7ff73c88fe8a
+	0x7ff73c8b1005
+	0x7ff73c5dd71e
+	0x7ff73c5e4e1f
+	0x7ff73c5cb7c4
+	0x7ff73c5cb97f
+	0x7ff73c5b18e8
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -3473,7 +3473,7 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>£40.53</t>
+          <t>Error: 500 Server Error: Internal Server Error for url: https://www.insulation-online.com/product/celotex-cw4100-100mm/</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -3488,7 +3488,7 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: 500 Server Error: Internal Server Error for url: https://www.directinsulation.com/product-page/celotex-cavity-cw4100-450mm-x-1200mm-pack-of-6</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
@@ -3535,7 +3535,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>£1248.0</t>
+          <t>Error: 500 Server Error: Internal Server Error for url: https://materialsmarket.com/products/90mm-celotex-thermaclass-cavity-wall-21-full-fill-insulation-board-t-g-1190mm-x-450mm-3-21m2-pack</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3550,7 +3550,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>£1172.16</t>
+          <t>Error: 'NoneType' object has no attribute 'find_all'</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -3570,7 +3570,7 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>£1057.71</t>
+          <t>Error: 500 Server Error: Internal Server Error for url: https://www.insulation-online.com/product/celotex-thermaclass-cavity-wall-21-90mm/</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>£1328.0</t>
+          <t>Error: 500 Server Error: Internal Server Error for url: https://materialsmarket.com/products/115mm-celotex-thermaclass-cavity-wall-21-full-fill-insulation-board-t-g-1190mm-x-450mm-2-68m2-pack</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3647,7 +3647,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>£1407.2</t>
+          <t>Error: 'NoneType' object has no attribute 'find_all'</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -3667,7 +3667,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>£1126.15</t>
+          <t>Error: 500 Server Error: Internal Server Error for url: https://www.insulation-online.com/product/celotex-thermaclass-cavity-wall-21-115mm/</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -3729,14 +3729,14 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
+          <t>Error: 500 Server Error: Internal Server Error for url: https://materialsmarket.com/products/140mm-celotex-thermaclass-cavity-wall-21-full-fill-insulation-board-t-g-1190mm-x-450mm-2-14m2-pack</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
           <t>£1280.0</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>£1280.0</t>
-        </is>
-      </c>
       <c r="I29" t="inlineStr">
         <is>
           <t>N/L</t>
@@ -3744,7 +3744,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>£1336.96</t>
+          <t>Error: 'NoneType' object has no attribute 'find_all'</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -3764,7 +3764,7 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>£1096.66</t>
+          <t>Error: 500 Server Error: Internal Server Error for url: https://www.insulation-online.com/product/celotex-thermaclass-cavity-wall-21-140mm/</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
